--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="28.5" customWidth="1" style="1" min="2" max="2"/>
@@ -1496,67 +1496,60 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="n">
-        <v>600001</v>
+        <v>500004</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>Effect_Buff_2</t>
+          <t>Effect_ShieldBubble_1</t>
         </is>
       </c>
       <c r="C14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="0" t="inlineStr">
-        <is>
-          <t>StartPosition:0,0.5,0+{StartPosition}</t>
-        </is>
-      </c>
-      <c r="I14" s="0" t="inlineStr">
-        <is>
-          <t>ColorEffect:1,1,1,1&amp;ColorSmoke:0.783,0.284,0.284,1</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t>魅惑</t>
+          <t>护罩穹顶罩体资源(shader预制,框架层 EffectShieldBubble 组件驱动,已接入大盾战士BOSS援护护盾)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="n">
-        <v>700001</v>
+        <v>600001</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>Effect_BodySlam_1</t>
+          <t>Effect_Buff_2</t>
         </is>
       </c>
       <c r="C15" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="0" t="inlineStr">
-        <is>
-          <t>Size:0.75*{Size}</t>
-        </is>
-      </c>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t>StartPosition:{StartPosition}</t>
+          <t>StartPosition:0,0.5,0+{StartPosition}</t>
+        </is>
+      </c>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>ColorEffect:1,1,1,1&amp;ColorSmoke:0.783,0.284,0.284,1</t>
         </is>
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t>地面打击</t>
+          <t>魅惑</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="n">
-        <v>800001</v>
+        <v>700001</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>Effect_PillarBlast_Fire_1</t>
+          <t>Effect_BodySlam_1</t>
         </is>
       </c>
       <c r="C16" s="0" t="n">
@@ -1564,7 +1557,7 @@
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
-          <t>Size:1.25*{Size}</t>
+          <t>Size:0.75*{Size}</t>
         </is>
       </c>
       <c r="H16" s="0" t="inlineStr">
@@ -1574,17 +1567,17 @@
       </c>
       <c r="J16" s="0" t="inlineStr">
         <is>
-          <t>火锥</t>
+          <t>地面打击</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="n">
-        <v>800002</v>
+        <v>800001</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>Effect_PillarBlast_Ice_1</t>
+          <t>Effect_PillarBlast_Fire_1</t>
         </is>
       </c>
       <c r="C17" s="0" t="n">
@@ -1602,38 +1595,45 @@
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t>冰锥</t>
+          <t>火锥</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="n">
-        <v>900001</v>
+        <v>800002</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>Effect_Thunder_1</t>
+          <t>Effect_PillarBlast_Ice_1</t>
         </is>
       </c>
       <c r="C18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="0" t="n">
-        <v>0.5</v>
+        <v>1</v>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>Size:1.25*{Size}</t>
+        </is>
+      </c>
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>StartPosition:{StartPosition}</t>
+        </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t>雷电连锁1</t>
+          <t>冰锥</t>
         </is>
       </c>
     </row>
     <row r="19" ht="12" customHeight="1" s="1">
       <c r="A19" s="0" t="n">
-        <v>900002</v>
+        <v>900001</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>Effect_Thunder_2</t>
+          <t>Effect_Thunder_1</t>
         </is>
       </c>
       <c r="C19" s="0" t="n">
@@ -1644,59 +1644,59 @@
       </c>
       <c r="J19" s="0" t="inlineStr">
         <is>
-          <t>雷电连锁2</t>
+          <t>雷电连锁1</t>
         </is>
       </c>
     </row>
     <row r="20" ht="12" customHeight="1" s="1">
       <c r="A20" s="0" t="n">
-        <v>900003</v>
+        <v>900002</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>Effect_Thunder_3</t>
+          <t>Effect_Thunder_2</t>
         </is>
       </c>
       <c r="C20" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t>落雷(全局单例,深渊馈赠闪电)</t>
+          <t>雷电连锁2</t>
         </is>
       </c>
     </row>
     <row r="21" ht="12" customHeight="1" s="1">
       <c r="A21" s="0" t="n">
-        <v>1000001</v>
+        <v>900003</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>Effect_Mana_1</t>
+          <t>Effect_Thunder_3</t>
         </is>
       </c>
       <c r="C21" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t>放置魔物-魔王消耗魔力</t>
+          <t>落雷(全局单例,深渊馈赠闪电)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="12" customHeight="1" s="1">
       <c r="A22" s="0" t="n">
-        <v>1100001</v>
+        <v>1000001</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>Effect_CreatureShow_1</t>
+          <t>Effect_Mana_1</t>
         </is>
       </c>
       <c r="C22" s="0" t="n">
@@ -1707,38 +1707,38 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t>放置魔物-生成登场</t>
+          <t>放置魔物-魔王消耗魔力</t>
         </is>
       </c>
     </row>
     <row r="23" ht="12" customHeight="1" s="1">
       <c r="A23" s="0" t="n">
-        <v>1200001</v>
+        <v>1100001</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>Effect_Blood_1</t>
+          <t>Effect_CreatureShow_1</t>
         </is>
       </c>
       <c r="C23" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t>受击溅血(高频)</t>
+          <t>放置魔物-生成登场</t>
         </is>
       </c>
     </row>
     <row r="24" ht="12" customHeight="1" s="1">
       <c r="A24" s="0" t="n">
-        <v>1300001</v>
+        <v>1200001</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>Effect_ShieldHit_1</t>
+          <t>Effect_Blood_1</t>
         </is>
       </c>
       <c r="C24" s="0" t="n">
@@ -1749,17 +1749,17 @@
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t>护盾打击(高频)</t>
+          <t>受击溅血(高频)</t>
         </is>
       </c>
     </row>
     <row r="25" ht="12" customHeight="1" s="1">
       <c r="A25" s="0" t="n">
-        <v>1400001</v>
+        <v>1300001</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>Effect_Move_1</t>
+          <t>Effect_ShieldHit_1</t>
         </is>
       </c>
       <c r="C25" s="0" t="n">
@@ -1770,148 +1770,169 @@
       </c>
       <c r="J25" s="0" t="inlineStr">
         <is>
-          <t>进阶增加进度</t>
+          <t>护盾打击(高频)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="12" customHeight="1" s="1">
       <c r="A26" s="0" t="n">
-        <v>1500001</v>
+        <v>1400001</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>Effect_AscendComplete_1</t>
+          <t>Effect_Move_1</t>
         </is>
       </c>
       <c r="C26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="0" t="n">
-        <v>2</v>
-      </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t>进阶完成庆祝</t>
+          <t>进阶增加进度</t>
         </is>
       </c>
     </row>
     <row r="27" ht="12" customHeight="1" s="1">
       <c r="A27" s="0" t="n">
-        <v>1600001</v>
+        <v>1500001</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>Effect_Trail_1</t>
+          <t>Effect_AscendComplete_1</t>
         </is>
       </c>
       <c r="C27" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27" s="0" t="inlineStr">
         <is>
-          <t>攻击弹道拖尾(方案2 VFX)</t>
+          <t>进阶完成庆祝</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="n">
-        <v>1700001</v>
+        <v>1600001</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>Effect_Shockwave_1</t>
+          <t>Effect_Trail_1</t>
         </is>
       </c>
       <c r="C28" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="0" t="n">
-        <v>4</v>
-      </c>
       <c r="J28" s="0" t="inlineStr">
         <is>
-          <t>冲击波(深渊馈赠第六次冲击,一次性,播放时由ShowShockwaveEffect同步半径/时长)</t>
+          <t>攻击弹道拖尾(方案2 VFX)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="n">
-        <v>1800001</v>
+        <v>1700001</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>Effect_FloorFire_1</t>
+          <t>Effect_Shockwave_1</t>
         </is>
       </c>
       <c r="C29" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E29" s="0" t="inlineStr"/>
-      <c r="F29" s="0" t="inlineStr"/>
-      <c r="G29" s="0" t="inlineStr"/>
-      <c r="H29" s="0" t="inlineStr"/>
-      <c r="I29" s="0" t="inlineStr"/>
+        <v>4</v>
+      </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t>地面火焰(深渊馈赠瓶装炼狱火,全局单例,播放时由ShowEnduringSingletonEffect(effect_hit击中粒子1800001)按燃烧时长重设主粒子duration)</t>
+          <t>冲击波(深渊馈赠第六次冲击,一次性,播放时由ShowShockwaveEffect同步半径/时长)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="n">
-        <v>1900001</v>
+        <v>1800001</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>Effect_Hit_1</t>
+          <t>Effect_FloorFire_1</t>
         </is>
       </c>
       <c r="C30" s="0" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E30" s="0" t="inlineStr"/>
+      <c r="F30" s="0" t="inlineStr"/>
+      <c r="G30" s="0" t="inlineStr"/>
+      <c r="H30" s="0" t="inlineStr"/>
+      <c r="I30" s="0" t="inlineStr"/>
       <c r="J30" s="0" t="inlineStr">
         <is>
-          <t>击中(通用,牛头人投手落点)</t>
+          <t>地面火焰(深渊馈赠瓶装炼狱火,全局单例,播放时由ShowEnduringSingletonEffect(effect_hit击中粒子1800001)按燃烧时长重设主粒子duration)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="n">
-        <v>2000001</v>
+        <v>1900001</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>Effect_Boom_Fire_2</t>
+          <t>Effect_Hit_1</t>
         </is>
       </c>
       <c r="C31" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="0" t="inlineStr">
         <is>
-          <t>火爆发(火大魔法师BOSS技能击中,全局单例)</t>
+          <t>击中(通用,牛头人投手落点)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="n">
-        <v>2000002</v>
+        <v>2000001</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>Effect_Boom_Water_2</t>
+          <t>Effect_Boom_Fire_2</t>
         </is>
       </c>
       <c r="C32" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="0" t="inlineStr">
+        <is>
+          <t>火爆发(火大魔法师BOSS技能击中,全局单例)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="n">
+        <v>2000002</v>
+      </c>
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t>Effect_Boom_Water_2</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="0" t="inlineStr">
         <is>
           <t>水爆发(水大魔法师BOSS技能击中,全局单例)</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_effect_info[粒子信息].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="28.5" customWidth="1" style="1" min="2" max="2"/>
@@ -1956,6 +1956,69 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="0" t="n">
+        <v>2100001</v>
+      </c>
+      <c r="B35" s="0" t="inlineStr">
+        <is>
+          <t>Effect_Hit_2</t>
+        </is>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="0" t="inlineStr">
+        <is>
+          <t>普攻击中-神圣瞬击(牧师普攻102003,一次性)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="n">
+        <v>2100002</v>
+      </c>
+      <c r="B36" s="0" t="inlineStr">
+        <is>
+          <t>Effect_Buff_Health_2</t>
+        </is>
+      </c>
+      <c r="C36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J36" s="0" t="inlineStr">
+        <is>
+          <t>单体治疗(牧师群体治疗500006,一次性独立实例)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2100003</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Effect_Buff_Health_3</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>5</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>范围治疗区域(神官技能500007,一次性独立实例,show_time=持续5秒)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
